--- a/模擬數據.xlsx
+++ b/模擬數據.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joe90\Desktop\NTU\4sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D88B626-FE18-40AD-81B5-2239921482CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E9E7BF-E610-4204-AC94-4F7583E35EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XOC_50um" sheetId="1" r:id="rId1"/>
     <sheet name="YOC_-20um" sheetId="2" r:id="rId2"/>
-    <sheet name="AOC_5.236mrad" sheetId="4" r:id="rId3"/>
-    <sheet name="BOA_3.4906mrad" sheetId="3" r:id="rId4"/>
+    <sheet name="AOC_0.3度" sheetId="4" r:id="rId3"/>
+    <sheet name="BOA_0.2度" sheetId="3" r:id="rId4"/>
+    <sheet name="ZOC_0.05mm" sheetId="5" r:id="rId5"/>
+    <sheet name="BOC_0.03度" sheetId="6" r:id="rId6"/>
+    <sheet name="XOA_0.05mm" sheetId="7" r:id="rId7"/>
+    <sheet name="YOA_0.05mm" sheetId="8" r:id="rId8"/>
+    <sheet name="ZOA_0.05mm" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="5">
   <si>
     <r>
       <t>A</t>
@@ -405,6 +410,251 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>328165</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>49841</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36C16F6E-0903-4ED7-B484-E79E77B6EAD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3620005" cy="2229161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>328165</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28856</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A97A785E-DBCC-4BED-A57D-8CDAFFA28208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3620005" cy="2010056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>442481</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA08F5E2-A9BA-45DE-B6DD-7D4F7EAA94F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3734321" cy="1991003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>299586</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2BF213F-C201-4E5F-9170-37CE3E2827A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3591426" cy="1991003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>299586</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38382</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5B2A51D-0BB0-458F-9C1B-4B71A9BC4A72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="693420"/>
+          <a:ext cx="3591426" cy="2019582"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2136,4 +2386,1865 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303D3177-1BC4-42A7-8E76-80FC4159664E}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>60</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2">
+        <v>120</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2">
+        <v>70</v>
+      </c>
+      <c r="C9" s="2">
+        <v>140</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2">
+        <v>160</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2">
+        <v>180</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2">
+        <v>80</v>
+      </c>
+      <c r="C12" s="2">
+        <v>200</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2">
+        <v>220</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2">
+        <v>240</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2">
+        <v>50</v>
+      </c>
+      <c r="C15" s="2">
+        <v>260</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2">
+        <v>280</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2">
+        <v>300</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2">
+        <v>320</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2">
+        <v>340</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>360</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFA25A1-737B-4FB7-89CF-0DBBF7B41C32}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.5789999999999998E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>8.9279999999999998E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-9.3399999999999993E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.1260000000000002E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.16652</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-3.4569999999999997E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.13092999999999999</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.22252</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-6.8089999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3">
+        <v>80</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.21637999999999999</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.25307000000000002</v>
+      </c>
+      <c r="F6" s="3">
+        <v>-9.9540000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.30731999999999998</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.25977</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-0.11863</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3">
+        <v>120</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.39278000000000002</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.24923000000000001</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-0.11792999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3">
+        <v>140</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.46245000000000003</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.23111999999999999</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-9.4979999999999995E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3">
+        <v>160</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.50792000000000004</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.21532999999999999</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-5.296E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3">
+        <v>180</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.52371000000000001</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.20916999999999999</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>80</v>
+      </c>
+      <c r="C12" s="3">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.50792000000000004</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.18423</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.12342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>70</v>
+      </c>
+      <c r="C13" s="3">
+        <v>220</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.46245000000000003</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.22131999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3">
+        <v>240</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.39278000000000002</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.248E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.27481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3">
+        <v>260</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.30731999999999998</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-7.1720000000000006E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.27642</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3">
+        <v>280</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.21637999999999999</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-0.14197000000000001</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.23194999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3">
+        <v>300</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.13092999999999999</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-0.17022000000000001</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.15866</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>320</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.1260000000000002E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-0.14978</v>
+      </c>
+      <c r="F18" s="3">
+        <v>8.0549999999999997E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>340</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.5789999999999998E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-8.7090000000000001E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.1760000000000002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>360</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78160755-31FB-4FEC-A755-D1AE39D0206A}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.6840000000000001E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-2.97E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-1.099E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3">
+        <v>80</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4.1320000000000003E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.7719999999999997E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>-3.1649999999999998E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.8680000000000003E-2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.1649999999999998E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-3.7719999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3">
+        <v>120</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3">
+        <v>140</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.099E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-3.0200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3">
+        <v>160</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.6979999999999997E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.97E-3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-1.6840000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3">
+        <v>180</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>80</v>
+      </c>
+      <c r="C12" s="3">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3">
+        <v>9.6979999999999997E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-2.97E-3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.6840000000000001E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>70</v>
+      </c>
+      <c r="C13" s="3">
+        <v>220</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-1.099E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3">
+        <v>240</v>
+      </c>
+      <c r="D14" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3">
+        <v>260</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5.8680000000000003E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-3.1649999999999998E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3.7719999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3">
+        <v>280</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.1320000000000003E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-3.7719999999999997E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.1649999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3">
+        <v>300</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-3.7499999999999999E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.1649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>320</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3.0200000000000001E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.099E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>340</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-1.6840000000000001E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.97E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>360</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25055C05-B10C-4482-AD22-291ABAE17B04}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.7299999999999998E-3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8.1600000000000006E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3">
+        <v>-3.2140000000000002E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.401E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.835E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3">
+        <v>80</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-4.9239999999999999E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.335E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.5799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-4.9239999999999999E-2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5.5579999999999997E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-6.6499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3">
+        <v>120</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3">
+        <v>140</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-3.2140000000000002E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-3.5990000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3">
+        <v>160</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.8160000000000003E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-4.6269999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3">
+        <v>180</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>80</v>
+      </c>
+      <c r="C12" s="3">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.8160000000000003E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-4.6269999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>70</v>
+      </c>
+      <c r="C13" s="3">
+        <v>220</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.2140000000000002E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-3.5990000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3">
+        <v>240</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3">
+        <v>260</v>
+      </c>
+      <c r="D15" s="3">
+        <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.5579999999999997E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-6.6499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3">
+        <v>280</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.335E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>5.5799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3">
+        <v>300</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.835E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>320</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.2140000000000002E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.401E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>340</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.7299999999999998E-3</v>
+      </c>
+      <c r="F19" s="3">
+        <v>8.1600000000000006E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>360</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54835BDA-D696-44E0-956C-FC6B32711DE1}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.7299999999999998E-3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8.1600000000000006E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3">
+        <v>-3.2140000000000002E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.401E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.835E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3">
+        <v>80</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-4.9239999999999999E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.335E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.5799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
+        <v>100</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-4.9239999999999999E-2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5.5579999999999997E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-6.6499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3">
+        <v>120</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3">
+        <v>140</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-3.2140000000000002E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-3.5990000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3">
+        <v>160</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.8160000000000003E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-4.6269999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3">
+        <v>180</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>80</v>
+      </c>
+      <c r="C12" s="3">
+        <v>200</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.8160000000000003E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-4.6269999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>70</v>
+      </c>
+      <c r="C13" s="3">
+        <v>220</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.2140000000000002E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-3.5990000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3">
+        <v>240</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3">
+        <v>260</v>
+      </c>
+      <c r="D15" s="3">
+        <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.5579999999999997E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-6.6499999999999997E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3">
+        <v>280</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.335E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>5.5799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3">
+        <v>300</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.835E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>320</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.2140000000000002E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.401E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3">
+        <v>340</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.7299999999999998E-3</v>
+      </c>
+      <c r="F19" s="3">
+        <v>8.1600000000000006E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>360</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/模擬數據.xlsx
+++ b/模擬數據.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joe90\Desktop\NTU\4sprint\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E9E7BF-E610-4204-AC94-4F7583E35EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441F9972-1A76-44FE-8D0B-1B74E27EBD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XOC_50um" sheetId="1" r:id="rId1"/>
     <sheet name="YOC_-20um" sheetId="2" r:id="rId2"/>
-    <sheet name="AOC_0.3度" sheetId="4" r:id="rId3"/>
-    <sheet name="BOA_0.2度" sheetId="3" r:id="rId4"/>
-    <sheet name="ZOC_0.05mm" sheetId="5" r:id="rId5"/>
-    <sheet name="BOC_0.03度" sheetId="6" r:id="rId6"/>
-    <sheet name="XOA_0.05mm" sheetId="7" r:id="rId7"/>
-    <sheet name="YOA_0.05mm" sheetId="8" r:id="rId8"/>
-    <sheet name="ZOA_0.05mm" sheetId="9" r:id="rId9"/>
+    <sheet name="ZOC_0.05mm" sheetId="5" r:id="rId3"/>
+    <sheet name="XOA_0.05mm" sheetId="7" r:id="rId4"/>
+    <sheet name="YOA_0.05mm" sheetId="8" r:id="rId5"/>
+    <sheet name="ZOA_0.05mm" sheetId="9" r:id="rId6"/>
+    <sheet name="AOC_0.3度" sheetId="4" r:id="rId7"/>
+    <sheet name="BOC_0.03度" sheetId="6" r:id="rId8"/>
+    <sheet name="BOA_0.2度" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="8">
   <si>
     <r>
       <t>A</t>
@@ -107,6 +108,18 @@
       <t>誤差</t>
     </r>
   </si>
+  <si>
+    <t>ZOA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -159,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -182,11 +195,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF4472C4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -196,6 +250,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -318,6 +381,208 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>328165</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>49841</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36C16F6E-0903-4ED7-B484-E79E77B6EAD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3620005" cy="2229161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>442481</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA08F5E2-A9BA-45DE-B6DD-7D4F7EAA94F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3734321" cy="1991003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>299586</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2BF213F-C201-4E5F-9170-37CE3E2827A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="1089660"/>
+          <a:ext cx="3591426" cy="1991003"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>375285</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="圖片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{301A918A-32D6-4F0B-8FC9-0958B843569B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3840480" y="693420"/>
+          <a:ext cx="3667125" cy="2009775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -361,105 +626,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>221245</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>85313</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266F0828-AA32-4F1D-BCEF-4856C08CCB68}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3840480" y="1089660"/>
-          <a:ext cx="4610365" cy="2462753"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>328165</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>49841</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36C16F6E-0903-4ED7-B484-E79E77B6EAD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3840480" y="1089660"/>
-          <a:ext cx="3620005" cy="2229161"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -508,7 +675,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -518,17 +685,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>442481</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>9803</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>221245</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85313</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="圖片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA08F5E2-A9BA-45DE-B6DD-7D4F7EAA94F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266F0828-AA32-4F1D-BCEF-4856C08CCB68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -545,105 +712,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3840480" y="1089660"/>
-          <a:ext cx="3734321" cy="1991003"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>299586</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>9803</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2BF213F-C201-4E5F-9170-37CE3E2827A3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3840480" y="1089660"/>
-          <a:ext cx="3591426" cy="1991003"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>299586</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>38382</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5B2A51D-0BB0-458F-9C1B-4B71A9BC4A72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3840480" y="693420"/>
-          <a:ext cx="3591426" cy="2019582"/>
+          <a:ext cx="4610365" cy="2462753"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1663,361 +1732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A12A91-1605-4EE0-85F1-D79D589C5526}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.89539999999999997</v>
-      </c>
-      <c r="E3" s="2">
-        <v>-0.21690000000000001</v>
-      </c>
-      <c r="F3" s="2">
-        <v>-0.32628000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2">
-        <v>40</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.6828099999999999</v>
-      </c>
-      <c r="E4" s="2">
-        <v>-0.80520999999999998</v>
-      </c>
-      <c r="F4" s="2">
-        <v>-0.42665999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2">
-        <v>30</v>
-      </c>
-      <c r="C5" s="2">
-        <v>60</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2.2672400000000001</v>
-      </c>
-      <c r="E5" s="2">
-        <v>-1.5884199999999999</v>
-      </c>
-      <c r="F5" s="2">
-        <v>-0.13803000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2">
-        <v>80</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2.5782099999999999</v>
-      </c>
-      <c r="E6" s="2">
-        <v>-2.3253300000000001</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.59014999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2">
-        <v>100</v>
-      </c>
-      <c r="D7" s="2">
-        <v>2.5782099999999999</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-2.7755899999999998</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1.6783999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2">
-        <v>60</v>
-      </c>
-      <c r="C8" s="2">
-        <v>120</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2.2672400000000001</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-2.7654700000000001</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2.9350299999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2">
-        <v>70</v>
-      </c>
-      <c r="C9" s="2">
-        <v>140</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1.6828099999999999</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-2.23597</v>
-      </c>
-      <c r="F9" s="2">
-        <v>4.1044299999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2">
-        <v>80</v>
-      </c>
-      <c r="C10" s="2">
-        <v>160</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.89539999999999997</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-1.2605299999999999</v>
-      </c>
-      <c r="F10" s="2">
-        <v>4.9331300000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="2">
-        <v>90</v>
-      </c>
-      <c r="C11" s="2">
-        <v>180</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-2.742E-2</v>
-      </c>
-      <c r="F11" s="2">
-        <v>5.2358900000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="2">
-        <v>80</v>
-      </c>
-      <c r="C12" s="2">
-        <v>200</v>
-      </c>
-      <c r="D12" s="2">
-        <v>-0.89539999999999997</v>
-      </c>
-      <c r="E12" s="2">
-        <v>-0.55542000000000002</v>
-      </c>
-      <c r="F12" s="2">
-        <v>5.0593599999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="B13" s="2">
-        <v>70</v>
-      </c>
-      <c r="C13" s="2">
-        <v>220</v>
-      </c>
-      <c r="D13" s="2">
-        <v>-1.6828099999999999</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-0.97211999999999998</v>
-      </c>
-      <c r="F13" s="2">
-        <v>4.5681799999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2">
-        <v>60</v>
-      </c>
-      <c r="C14" s="2">
-        <v>240</v>
-      </c>
-      <c r="D14" s="2">
-        <v>-2.2672400000000001</v>
-      </c>
-      <c r="E14" s="2">
-        <v>-1.19706</v>
-      </c>
-      <c r="F14" s="2">
-        <v>3.8460299999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2">
-        <v>50</v>
-      </c>
-      <c r="C15" s="2">
-        <v>260</v>
-      </c>
-      <c r="D15" s="2">
-        <v>-2.5782099999999999</v>
-      </c>
-      <c r="E15" s="2">
-        <v>-1.1990499999999999</v>
-      </c>
-      <c r="F15" s="2">
-        <v>3.0083299999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2">
-        <v>40</v>
-      </c>
-      <c r="C16" s="2">
-        <v>280</v>
-      </c>
-      <c r="D16" s="2">
-        <v>-2.5782099999999999</v>
-      </c>
-      <c r="E16" s="2">
-        <v>-1.0036700000000001</v>
-      </c>
-      <c r="F16" s="2">
-        <v>2.1736399999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2">
-        <v>30</v>
-      </c>
-      <c r="C17" s="2">
-        <v>300</v>
-      </c>
-      <c r="D17" s="2">
-        <v>-2.2672400000000001</v>
-      </c>
-      <c r="E17" s="2">
-        <v>-0.68564000000000003</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1.43513</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2">
-        <v>320</v>
-      </c>
-      <c r="D18" s="2">
-        <v>-1.6828099999999999</v>
-      </c>
-      <c r="E18" s="2">
-        <v>-0.34808</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0.83960000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="2">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2">
-        <v>340</v>
-      </c>
-      <c r="D19" s="2">
-        <v>-0.89539999999999997</v>
-      </c>
-      <c r="E19" s="2">
-        <v>-9.4359999999999999E-2</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.37947999999999998</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5A132A-88CF-427F-B733-0730984EDA41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303D3177-1BC4-42A7-8E76-80FC4159664E}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2040,344 +1755,717 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>60</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2">
+        <v>120</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2">
+        <v>70</v>
+      </c>
+      <c r="C9" s="2">
+        <v>140</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2">
+        <v>160</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2">
+        <v>180</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2">
+        <v>80</v>
+      </c>
+      <c r="C12" s="2">
+        <v>200</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2">
+        <v>220</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2">
+        <v>240</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2">
+        <v>50</v>
+      </c>
+      <c r="C15" s="2">
+        <v>260</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2">
+        <v>280</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2">
+        <v>300</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2">
+        <v>320</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2">
+        <v>340</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>360</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78160755-31FB-4FEC-A755-D1AE39D0206A}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>20</v>
       </c>
-      <c r="D3" s="2">
-        <v>1.49E-3</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1.1390000000000001E-2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>-1E-3</v>
+      <c r="D3" s="3">
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.6840000000000001E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-2.97E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>20</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>40</v>
       </c>
-      <c r="D4" s="2">
-        <v>4.8199999999999996E-3</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.8280000000000001E-2</v>
-      </c>
-      <c r="F4" s="2">
-        <v>-3.2200000000000002E-3</v>
+      <c r="D4" s="3">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-1.099E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>30</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>60</v>
       </c>
-      <c r="D5" s="2">
-        <v>6.8500000000000002E-3</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.7440000000000001E-2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>-4.6699999999999997E-3</v>
+      <c r="D5" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-2.1649999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>40</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>80</v>
       </c>
-      <c r="D6" s="2">
-        <v>3.3600000000000001E-3</v>
-      </c>
-      <c r="E6" s="2">
-        <v>7.77E-3</v>
-      </c>
-      <c r="F6" s="2">
-        <v>-2.8300000000000001E-3</v>
+      <c r="D6" s="3">
+        <v>4.1320000000000003E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.7719999999999997E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>-3.1649999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>50</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>100</v>
       </c>
-      <c r="D7" s="2">
-        <v>-9.6799999999999994E-3</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-9.3100000000000006E-3</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4.3400000000000001E-3</v>
+      <c r="D7" s="3">
+        <v>5.8680000000000003E-2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.1649999999999998E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-3.7719999999999997E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>60</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>120</v>
       </c>
-      <c r="D8" s="2">
-        <v>-3.49E-2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-3.0259999999999999E-2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1.7469999999999999E-2</v>
+      <c r="D8" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-3.7499999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>70</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>140</v>
       </c>
-      <c r="D9" s="2">
-        <v>-7.2660000000000002E-2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-5.0279999999999998E-2</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3.5220000000000001E-2</v>
+      <c r="D9" s="3">
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.099E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-3.0200000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>80</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>160</v>
       </c>
-      <c r="D10" s="2">
-        <v>-0.12069000000000001</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-6.4640000000000003E-2</v>
-      </c>
-      <c r="F10" s="2">
-        <v>5.4260000000000003E-2</v>
+      <c r="D10" s="3">
+        <v>9.6979999999999997E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.97E-3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-1.6840000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>90</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>180</v>
       </c>
-      <c r="D11" s="2">
-        <v>-0.17451</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-6.9839999999999999E-2</v>
-      </c>
-      <c r="F11" s="2">
-        <v>6.9870000000000002E-2</v>
+      <c r="D11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>80</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>200</v>
       </c>
-      <c r="D12" s="2">
-        <v>-0.16772000000000001</v>
-      </c>
-      <c r="E12" s="2">
-        <v>-6.4640000000000003E-2</v>
-      </c>
-      <c r="F12" s="2">
-        <v>5.4269999999999999E-2</v>
+      <c r="D12" s="3">
+        <v>9.6979999999999997E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-2.97E-3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.6840000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>70</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>220</v>
       </c>
-      <c r="D13" s="2">
-        <v>-0.157</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-5.0279999999999998E-2</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3.524E-2</v>
+      <c r="D13" s="3">
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-1.099E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.0200000000000001E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>60</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>240</v>
       </c>
-      <c r="D14" s="2">
-        <v>-0.13961999999999999</v>
-      </c>
-      <c r="E14" s="2">
-        <v>-3.0259999999999999E-2</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1.7489999999999999E-2</v>
+      <c r="D14" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-2.1649999999999999E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.7499999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>50</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>260</v>
       </c>
-      <c r="D15" s="2">
-        <v>-0.11501</v>
-      </c>
-      <c r="E15" s="2">
-        <v>-9.3100000000000006E-3</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4.3600000000000002E-3</v>
+      <c r="D15" s="3">
+        <v>5.8680000000000003E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-3.1649999999999998E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3.7719999999999997E-2</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>40</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>280</v>
       </c>
-      <c r="D16" s="2">
-        <v>-8.5029999999999994E-2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>7.77E-3</v>
-      </c>
-      <c r="F16" s="2">
-        <v>-2.81E-3</v>
+      <c r="D16" s="3">
+        <v>4.1320000000000003E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-3.7719999999999997E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.1649999999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>30</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>300</v>
       </c>
-      <c r="D17" s="2">
-        <v>-5.3609999999999998E-2</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1.7440000000000001E-2</v>
-      </c>
-      <c r="F17" s="2">
-        <v>-4.6600000000000001E-3</v>
+      <c r="D17" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-3.7499999999999999E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.1649999999999999E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>20</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>320</v>
       </c>
-      <c r="D18" s="2">
-        <v>-2.5870000000000001E-2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1.8280000000000001E-2</v>
-      </c>
-      <c r="F18" s="2">
-        <v>-3.2200000000000002E-3</v>
+      <c r="D18" s="3">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3.0200000000000001E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.099E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>10</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>340</v>
       </c>
-      <c r="D19" s="2">
-        <v>-6.7999999999999996E-3</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1.1390000000000001E-2</v>
-      </c>
-      <c r="F19" s="2">
-        <v>-1E-3</v>
+      <c r="D19" s="3">
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-1.6840000000000001E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.97E-3</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
-      <c r="B20" s="2">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
         <v>360</v>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2389,7 +2477,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303D3177-1BC4-42A7-8E76-80FC4159664E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25055C05-B10C-4482-AD22-291ABAE17B04}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2412,344 +2500,718 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>20</v>
       </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
+      <c r="D3" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.7299999999999998E-3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>8.1600000000000006E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
         <v>20</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>40</v>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
+      <c r="D4" s="3">
+        <v>-3.2140000000000002E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.401E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.3100000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
         <v>30</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>60</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
+      <c r="D5" s="3">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.835E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
         <v>40</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>80</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
+      <c r="D6" s="3">
+        <v>-4.9239999999999999E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4.335E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.5799999999999999E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
         <v>50</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>100</v>
       </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
+      <c r="D7" s="3">
+        <v>-4.9239999999999999E-2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5.5579999999999997E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-6.6499999999999997E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
         <v>60</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>120</v>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
+      <c r="D8" s="3">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-2.1649999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
         <v>70</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>140</v>
       </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
+      <c r="D9" s="3">
+        <v>-3.2140000000000002E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-3.5990000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
         <v>80</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>160</v>
       </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
+      <c r="D10" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.8160000000000003E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-4.6269999999999999E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
         <v>90</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>180</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
         <v>80</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>200</v>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
+      <c r="D12" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.8160000000000003E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-4.6269999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
         <v>70</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>220</v>
       </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
+      <c r="D13" s="3">
+        <v>3.2140000000000002E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-3.5990000000000001E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
         <v>60</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>240</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-2.1649999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
         <v>50</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>260</v>
       </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="D15" s="3">
+        <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.5579999999999997E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-6.6499999999999997E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
         <v>40</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>280</v>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
+      <c r="D16" s="3">
+        <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.335E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>5.5799999999999999E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
         <v>30</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>300</v>
       </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
+      <c r="D17" s="3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.835E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
         <v>20</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>320</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
+      <c r="D18" s="3">
+        <v>3.2140000000000002E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.401E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.3100000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
         <v>10</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>340</v>
       </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
+      <c r="D19" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.7299999999999998E-3</v>
+      </c>
+      <c r="F19" s="3">
+        <v>8.1600000000000006E-3</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
         <v>360</v>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54835BDA-D696-44E0-956C-FC6B32711DE1}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>-8.6999999999999994E-3</v>
+      </c>
+      <c r="F3" s="6">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4">
+        <v>40</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="F4" s="6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>60</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4">
+        <v>80</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>-3.2099999999999997E-2</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1.17E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-3.8300000000000001E-2</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1.7899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>60</v>
+      </c>
+      <c r="C8" s="4">
+        <v>120</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>70</v>
+      </c>
+      <c r="C9" s="4">
+        <v>140</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-4.7E-2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>3.2899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>80</v>
+      </c>
+      <c r="C10" s="4">
+        <v>160</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-4.9200000000000001E-2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>4.1300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>90</v>
+      </c>
+      <c r="C11" s="4">
+        <v>180</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.05</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>80</v>
+      </c>
+      <c r="C12" s="4">
+        <v>200</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-4.9200000000000001E-2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>4.1300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>70</v>
+      </c>
+      <c r="C13" s="4">
+        <v>220</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-4.7E-2</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3.2899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>60</v>
+      </c>
+      <c r="C14" s="4">
+        <v>240</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-4.3299999999999998E-2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="4">
+        <v>260</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-3.8300000000000001E-2</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1.7899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4">
+        <v>280</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-3.2099999999999997E-2</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1.17E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4">
+        <v>300</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="F17" s="6">
+        <v>6.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4">
+        <v>320</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.7100000000000001E-2</v>
+      </c>
+      <c r="F18" s="6">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>340</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-8.6999999999999994E-3</v>
+      </c>
+      <c r="F19" s="6">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>360</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2761,9 +3223,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFA25A1-737B-4FB7-89CF-0DBBF7B41C32}">
-  <dimension ref="A1:F20"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A12A91-1605-4EE0-85F1-D79D589C5526}">
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2786,716 +3248,326 @@
     </row>
     <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>20</v>
       </c>
-      <c r="D3" s="3">
-        <v>1.5789999999999998E-2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>8.9279999999999998E-2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>-9.3399999999999993E-3</v>
+      <c r="D3" s="2">
+        <v>0.89539999999999997</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-0.21690000000000001</v>
+      </c>
+      <c r="F3" s="2">
+        <v>-0.32628000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>20</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>40</v>
       </c>
-      <c r="D4" s="3">
-        <v>6.1260000000000002E-2</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.16652</v>
-      </c>
-      <c r="F4" s="3">
-        <v>-3.4569999999999997E-2</v>
+      <c r="D4" s="2">
+        <v>1.6828099999999999</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-0.80520999999999998</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-0.42665999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>30</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>60</v>
       </c>
-      <c r="D5" s="3">
-        <v>0.13092999999999999</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.22252</v>
-      </c>
-      <c r="F5" s="3">
-        <v>-6.8089999999999998E-2</v>
+      <c r="D5" s="2">
+        <v>2.2672400000000001</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-1.5884199999999999</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-0.13803000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>40</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>80</v>
       </c>
-      <c r="D6" s="3">
-        <v>0.21637999999999999</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.25307000000000002</v>
-      </c>
-      <c r="F6" s="3">
-        <v>-9.9540000000000003E-2</v>
+      <c r="D6" s="2">
+        <v>2.5782099999999999</v>
+      </c>
+      <c r="E6" s="2">
+        <v>-2.3253300000000001</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.59014999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>50</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>100</v>
       </c>
-      <c r="D7" s="3">
-        <v>0.30731999999999998</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.25977</v>
-      </c>
-      <c r="F7" s="3">
-        <v>-0.11863</v>
+      <c r="D7" s="2">
+        <v>2.5782099999999999</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-2.7755899999999998</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.6783999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>60</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>120</v>
       </c>
-      <c r="D8" s="3">
-        <v>0.39278000000000002</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.24923000000000001</v>
-      </c>
-      <c r="F8" s="3">
-        <v>-0.11792999999999999</v>
+      <c r="D8" s="2">
+        <v>2.2672400000000001</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-2.7654700000000001</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2.9350299999999998</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>70</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>140</v>
       </c>
-      <c r="D9" s="3">
-        <v>0.46245000000000003</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.23111999999999999</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-9.4979999999999995E-2</v>
+      <c r="D9" s="2">
+        <v>1.6828099999999999</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-2.23597</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4.1044299999999998</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>80</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>160</v>
       </c>
-      <c r="D10" s="3">
-        <v>0.50792000000000004</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0.21532999999999999</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-5.296E-2</v>
+      <c r="D10" s="2">
+        <v>0.89539999999999997</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-1.2605299999999999</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4.9331300000000002</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>90</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>180</v>
       </c>
-      <c r="D11" s="3">
-        <v>0.52371000000000001</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0.20916999999999999</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-2.742E-2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5.2358900000000004</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>80</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>200</v>
       </c>
-      <c r="D12" s="3">
-        <v>0.50792000000000004</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0.18423</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.12342</v>
+      <c r="D12" s="2">
+        <v>-0.89539999999999997</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-0.55542000000000002</v>
+      </c>
+      <c r="F12" s="2">
+        <v>5.0593599999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>70</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>220</v>
       </c>
-      <c r="D13" s="3">
-        <v>0.46245000000000003</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.22131999999999999</v>
+      <c r="D13" s="2">
+        <v>-1.6828099999999999</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-0.97211999999999998</v>
+      </c>
+      <c r="F13" s="2">
+        <v>4.5681799999999999</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>60</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>240</v>
       </c>
-      <c r="D14" s="3">
-        <v>0.39278000000000002</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2.248E-2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.27481</v>
+      <c r="D14" s="2">
+        <v>-2.2672400000000001</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-1.19706</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3.8460299999999998</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>50</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>260</v>
       </c>
-      <c r="D15" s="3">
-        <v>0.30731999999999998</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-7.1720000000000006E-2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.27642</v>
+      <c r="D15" s="2">
+        <v>-2.5782099999999999</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-1.1990499999999999</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3.0083299999999999</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>40</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>280</v>
       </c>
-      <c r="D16" s="3">
-        <v>0.21637999999999999</v>
-      </c>
-      <c r="E16" s="3">
-        <v>-0.14197000000000001</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.23194999999999999</v>
+      <c r="D16" s="2">
+        <v>-2.5782099999999999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>-1.0036700000000001</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.1736399999999998</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <v>30</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>300</v>
       </c>
-      <c r="D17" s="3">
-        <v>0.13092999999999999</v>
-      </c>
-      <c r="E17" s="3">
-        <v>-0.17022000000000001</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.15866</v>
+      <c r="D17" s="2">
+        <v>-2.2672400000000001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>-0.68564000000000003</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.43513</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>20</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>320</v>
       </c>
-      <c r="D18" s="3">
-        <v>6.1260000000000002E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-0.14978</v>
-      </c>
-      <c r="F18" s="3">
-        <v>8.0549999999999997E-2</v>
+      <c r="D18" s="2">
+        <v>-1.6828099999999999</v>
+      </c>
+      <c r="E18" s="2">
+        <v>-0.34808</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.83960000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>10</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>340</v>
       </c>
-      <c r="D19" s="3">
-        <v>1.5789999999999998E-2</v>
-      </c>
-      <c r="E19" s="3">
-        <v>-8.7090000000000001E-2</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2.1760000000000002E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3">
-        <v>360</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78160755-31FB-4FEC-A755-D1AE39D0206A}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3">
-        <v>3.0200000000000001E-3</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1.6840000000000001E-2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>-2.97E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3">
-        <v>40</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1.17E-2</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3.0200000000000001E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>-1.099E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3">
-        <v>30</v>
-      </c>
-      <c r="C5" s="3">
-        <v>60</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>-2.1649999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3">
-        <v>40</v>
-      </c>
-      <c r="C6" s="3">
-        <v>80</v>
-      </c>
-      <c r="D6" s="3">
-        <v>4.1320000000000003E-2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>3.7719999999999997E-2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>-3.1649999999999998E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3">
-        <v>100</v>
-      </c>
-      <c r="D7" s="3">
-        <v>5.8680000000000003E-2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3.1649999999999998E-2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>-3.7719999999999997E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3">
-        <v>60</v>
-      </c>
-      <c r="C8" s="3">
-        <v>120</v>
-      </c>
-      <c r="D8" s="3">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2.1649999999999999E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>-3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3">
-        <v>140</v>
-      </c>
-      <c r="D9" s="3">
-        <v>8.8300000000000003E-2</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1.099E-2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-3.0200000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3">
-        <v>80</v>
-      </c>
-      <c r="C10" s="3">
-        <v>160</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9.6979999999999997E-2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2.97E-3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-1.6840000000000001E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3">
-        <v>90</v>
-      </c>
-      <c r="C11" s="3">
-        <v>180</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3">
-        <v>80</v>
-      </c>
-      <c r="C12" s="3">
-        <v>200</v>
-      </c>
-      <c r="D12" s="3">
-        <v>9.6979999999999997E-2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>-2.97E-3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1.6840000000000001E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3">
-        <v>70</v>
-      </c>
-      <c r="C13" s="3">
-        <v>220</v>
-      </c>
-      <c r="D13" s="3">
-        <v>8.8300000000000003E-2</v>
-      </c>
-      <c r="E13" s="3">
-        <v>-1.099E-2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>3.0200000000000001E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3">
-        <v>60</v>
-      </c>
-      <c r="C14" s="3">
-        <v>240</v>
-      </c>
-      <c r="D14" s="3">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-2.1649999999999999E-2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3">
-        <v>50</v>
-      </c>
-      <c r="C15" s="3">
-        <v>260</v>
-      </c>
-      <c r="D15" s="3">
-        <v>5.8680000000000003E-2</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-3.1649999999999998E-2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3.7719999999999997E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3">
-        <v>280</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4.1320000000000003E-2</v>
-      </c>
-      <c r="E16" s="3">
-        <v>-3.7719999999999997E-2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>3.1649999999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3">
-        <v>30</v>
-      </c>
-      <c r="C17" s="3">
-        <v>300</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>-3.7499999999999999E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2.1649999999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3">
-        <v>20</v>
-      </c>
-      <c r="C18" s="3">
-        <v>320</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1.17E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-3.0200000000000001E-2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1.099E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3">
-        <v>340</v>
-      </c>
-      <c r="D19" s="3">
-        <v>3.0200000000000001E-3</v>
-      </c>
-      <c r="E19" s="3">
-        <v>-1.6840000000000001E-2</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2.97E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3">
-        <v>360</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="D19" s="2">
+        <v>-0.89539999999999997</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-9.4359999999999999E-2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.37947999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -3506,12 +3578,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25055C05-B10C-4482-AD22-291ABAE17B04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFA25A1-737B-4FB7-89CF-0DBBF7B41C32}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:6" ht="46.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3555,13 +3632,13 @@
         <v>20</v>
       </c>
       <c r="D3" s="3">
-        <v>-1.7100000000000001E-2</v>
+        <v>1.5789999999999998E-2</v>
       </c>
       <c r="E3" s="3">
-        <v>3.7299999999999998E-3</v>
+        <v>8.9279999999999998E-2</v>
       </c>
       <c r="F3" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>-9.3399999999999993E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3573,13 +3650,13 @@
         <v>40</v>
       </c>
       <c r="D4" s="3">
-        <v>-3.2140000000000002E-2</v>
+        <v>6.1260000000000002E-2</v>
       </c>
       <c r="E4" s="3">
-        <v>1.401E-2</v>
+        <v>0.16652</v>
       </c>
       <c r="F4" s="3">
-        <v>1.3100000000000001E-2</v>
+        <v>-3.4569999999999997E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3591,13 +3668,13 @@
         <v>60</v>
       </c>
       <c r="D5" s="3">
-        <v>-4.3299999999999998E-2</v>
+        <v>0.13092999999999999</v>
       </c>
       <c r="E5" s="3">
-        <v>2.835E-2</v>
+        <v>0.22252</v>
       </c>
       <c r="F5" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>-6.8089999999999998E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3609,13 +3686,13 @@
         <v>80</v>
       </c>
       <c r="D6" s="3">
-        <v>-4.9239999999999999E-2</v>
+        <v>0.21637999999999999</v>
       </c>
       <c r="E6" s="3">
-        <v>4.335E-2</v>
+        <v>0.25307000000000002</v>
       </c>
       <c r="F6" s="3">
-        <v>5.5799999999999999E-3</v>
+        <v>-9.9540000000000003E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3627,13 +3704,13 @@
         <v>100</v>
       </c>
       <c r="D7" s="3">
-        <v>-4.9239999999999999E-2</v>
+        <v>0.30731999999999998</v>
       </c>
       <c r="E7" s="3">
-        <v>5.5579999999999997E-2</v>
+        <v>0.25977</v>
       </c>
       <c r="F7" s="3">
-        <v>-6.6499999999999997E-3</v>
+        <v>-0.11863</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3645,13 +3722,13 @@
         <v>120</v>
       </c>
       <c r="D8" s="3">
-        <v>-4.3299999999999998E-2</v>
+        <v>0.39278000000000002</v>
       </c>
       <c r="E8" s="3">
-        <v>6.25E-2</v>
+        <v>0.24923000000000001</v>
       </c>
       <c r="F8" s="3">
-        <v>-2.1649999999999999E-2</v>
+        <v>-0.11792999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3663,13 +3740,13 @@
         <v>140</v>
       </c>
       <c r="D9" s="3">
-        <v>-3.2140000000000002E-2</v>
+        <v>0.46245000000000003</v>
       </c>
       <c r="E9" s="3">
-        <v>6.3100000000000003E-2</v>
+        <v>0.23111999999999999</v>
       </c>
       <c r="F9" s="3">
-        <v>-3.5990000000000001E-2</v>
+        <v>-9.4979999999999995E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3681,13 +3758,13 @@
         <v>160</v>
       </c>
       <c r="D10" s="3">
-        <v>-1.7100000000000001E-2</v>
+        <v>0.50792000000000004</v>
       </c>
       <c r="E10" s="3">
-        <v>5.8160000000000003E-2</v>
+        <v>0.21532999999999999</v>
       </c>
       <c r="F10" s="3">
-        <v>-4.6269999999999999E-2</v>
+        <v>-5.296E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3699,13 +3776,13 @@
         <v>180</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>0.52371000000000001</v>
       </c>
       <c r="E11" s="3">
-        <v>0.05</v>
+        <v>0.20916999999999999</v>
       </c>
       <c r="F11" s="3">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3717,13 +3794,13 @@
         <v>200</v>
       </c>
       <c r="D12" s="3">
-        <v>1.7100000000000001E-2</v>
+        <v>0.50792000000000004</v>
       </c>
       <c r="E12" s="3">
-        <v>5.8160000000000003E-2</v>
+        <v>0.18423</v>
       </c>
       <c r="F12" s="3">
-        <v>-4.6269999999999999E-2</v>
+        <v>0.12342</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3735,13 +3812,13 @@
         <v>220</v>
       </c>
       <c r="D13" s="3">
-        <v>3.2140000000000002E-2</v>
+        <v>0.46245000000000003</v>
       </c>
       <c r="E13" s="3">
-        <v>6.3100000000000003E-2</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="F13" s="3">
-        <v>-3.5990000000000001E-2</v>
+        <v>0.22131999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3753,13 +3830,13 @@
         <v>240</v>
       </c>
       <c r="D14" s="3">
-        <v>4.3299999999999998E-2</v>
+        <v>0.39278000000000002</v>
       </c>
       <c r="E14" s="3">
-        <v>6.25E-2</v>
+        <v>2.248E-2</v>
       </c>
       <c r="F14" s="3">
-        <v>-2.1649999999999999E-2</v>
+        <v>0.27481</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3771,13 +3848,13 @@
         <v>260</v>
       </c>
       <c r="D15" s="3">
-        <v>4.9239999999999999E-2</v>
+        <v>0.30731999999999998</v>
       </c>
       <c r="E15" s="3">
-        <v>5.5579999999999997E-2</v>
+        <v>-7.1720000000000006E-2</v>
       </c>
       <c r="F15" s="3">
-        <v>-6.6499999999999997E-3</v>
+        <v>0.27642</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3789,13 +3866,13 @@
         <v>280</v>
       </c>
       <c r="D16" s="3">
-        <v>4.9239999999999999E-2</v>
+        <v>0.21637999999999999</v>
       </c>
       <c r="E16" s="3">
-        <v>4.335E-2</v>
+        <v>-0.14197000000000001</v>
       </c>
       <c r="F16" s="3">
-        <v>5.5799999999999999E-3</v>
+        <v>0.23194999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3807,13 +3884,13 @@
         <v>300</v>
       </c>
       <c r="D17" s="3">
-        <v>4.3299999999999998E-2</v>
+        <v>0.13092999999999999</v>
       </c>
       <c r="E17" s="3">
-        <v>2.835E-2</v>
+        <v>-0.17022000000000001</v>
       </c>
       <c r="F17" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>0.15866</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3825,13 +3902,13 @@
         <v>320</v>
       </c>
       <c r="D18" s="3">
-        <v>3.2140000000000002E-2</v>
+        <v>6.1260000000000002E-2</v>
       </c>
       <c r="E18" s="3">
-        <v>1.401E-2</v>
+        <v>-0.14978</v>
       </c>
       <c r="F18" s="3">
-        <v>1.3100000000000001E-2</v>
+        <v>8.0549999999999997E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3843,13 +3920,13 @@
         <v>340</v>
       </c>
       <c r="D19" s="3">
-        <v>1.7100000000000001E-2</v>
+        <v>1.5789999999999998E-2</v>
       </c>
       <c r="E19" s="3">
-        <v>3.7299999999999998E-3</v>
+        <v>-8.7090000000000001E-2</v>
       </c>
       <c r="F19" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>2.1760000000000002E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -3873,17 +3950,23 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54835BDA-D696-44E0-956C-FC6B32711DE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5A132A-88CF-427F-B733-0730984EDA41}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:6" ht="46.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3902,349 +3985,350 @@
     </row>
     <row r="2" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>20</v>
       </c>
-      <c r="D3" s="3">
-        <v>-1.7100000000000001E-2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>3.7299999999999998E-3</v>
-      </c>
-      <c r="F3" s="3">
-        <v>8.1600000000000006E-3</v>
+      <c r="D3" s="2">
+        <v>1.49E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1.1390000000000001E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>-1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>20</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>40</v>
       </c>
-      <c r="D4" s="3">
-        <v>-3.2140000000000002E-2</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1.401E-2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1.3100000000000001E-2</v>
+      <c r="D4" s="2">
+        <v>4.8199999999999996E-3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.8280000000000001E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-3.2200000000000002E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>30</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>60</v>
       </c>
-      <c r="D5" s="3">
-        <v>-4.3299999999999998E-2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2.835E-2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.2500000000000001E-2</v>
+      <c r="D5" s="2">
+        <v>6.8500000000000002E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.7440000000000001E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-4.6699999999999997E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>40</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>80</v>
       </c>
-      <c r="D6" s="3">
-        <v>-4.9239999999999999E-2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>4.335E-2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>5.5799999999999999E-3</v>
+      <c r="D6" s="2">
+        <v>3.3600000000000001E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7.77E-3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-2.8300000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>50</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>100</v>
       </c>
-      <c r="D7" s="3">
-        <v>-4.9239999999999999E-2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5.5579999999999997E-2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>-6.6499999999999997E-3</v>
+      <c r="D7" s="2">
+        <v>-9.6799999999999994E-3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-9.3100000000000006E-3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4.3400000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>60</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>120</v>
       </c>
-      <c r="D8" s="3">
-        <v>-4.3299999999999998E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>-2.1649999999999999E-2</v>
+      <c r="D8" s="2">
+        <v>-3.49E-2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-3.0259999999999999E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.7469999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>70</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>140</v>
       </c>
-      <c r="D9" s="3">
-        <v>-3.2140000000000002E-2</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6.3100000000000003E-2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-3.5990000000000001E-2</v>
+      <c r="D9" s="2">
+        <v>-7.2660000000000002E-2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-5.0279999999999998E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3.5220000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>80</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>160</v>
       </c>
-      <c r="D10" s="3">
-        <v>-1.7100000000000001E-2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5.8160000000000003E-2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-4.6269999999999999E-2</v>
+      <c r="D10" s="2">
+        <v>-0.12069000000000001</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-6.4640000000000003E-2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5.4260000000000003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>90</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>180</v>
       </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-0.05</v>
+      <c r="D11" s="2">
+        <v>-0.17451</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-6.9839999999999999E-2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6.9870000000000002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>80</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>200</v>
       </c>
-      <c r="D12" s="3">
-        <v>1.7100000000000001E-2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5.8160000000000003E-2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>-4.6269999999999999E-2</v>
+      <c r="D12" s="2">
+        <v>-0.16772000000000001</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-6.4640000000000003E-2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>5.4269999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>70</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>220</v>
       </c>
-      <c r="D13" s="3">
-        <v>3.2140000000000002E-2</v>
-      </c>
-      <c r="E13" s="3">
-        <v>6.3100000000000003E-2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-3.5990000000000001E-2</v>
+      <c r="D13" s="2">
+        <v>-0.157</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-5.0279999999999998E-2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3.524E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>60</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>240</v>
       </c>
-      <c r="D14" s="3">
-        <v>4.3299999999999998E-2</v>
-      </c>
-      <c r="E14" s="3">
-        <v>6.25E-2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-2.1649999999999999E-2</v>
+      <c r="D14" s="2">
+        <v>-0.13961999999999999</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-3.0259999999999999E-2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.7489999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>50</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>260</v>
       </c>
-      <c r="D15" s="3">
-        <v>4.9239999999999999E-2</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5.5579999999999997E-2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-6.6499999999999997E-3</v>
+      <c r="D15" s="2">
+        <v>-0.11501</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-9.3100000000000006E-3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>4.3600000000000002E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>40</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>280</v>
       </c>
-      <c r="D16" s="3">
-        <v>4.9239999999999999E-2</v>
-      </c>
-      <c r="E16" s="3">
-        <v>4.335E-2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>5.5799999999999999E-3</v>
+      <c r="D16" s="2">
+        <v>-8.5029999999999994E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>7.77E-3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-2.81E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <v>30</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>300</v>
       </c>
-      <c r="D17" s="3">
-        <v>4.3299999999999998E-2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2.835E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1.2500000000000001E-2</v>
+      <c r="D17" s="2">
+        <v>-5.3609999999999998E-2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.7440000000000001E-2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-4.6600000000000001E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>20</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>320</v>
       </c>
-      <c r="D18" s="3">
-        <v>3.2140000000000002E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1.401E-2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1.3100000000000001E-2</v>
+      <c r="D18" s="2">
+        <v>-2.5870000000000001E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.8280000000000001E-2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-3.2200000000000002E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>10</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>340</v>
       </c>
-      <c r="D19" s="3">
-        <v>1.7100000000000001E-2</v>
-      </c>
-      <c r="E19" s="3">
-        <v>3.7299999999999998E-3</v>
-      </c>
-      <c r="F19" s="3">
-        <v>8.1600000000000006E-3</v>
+      <c r="D19" s="2">
+        <v>-6.7999999999999996E-3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.1390000000000001E-2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-1E-3</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="2">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
         <v>360</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>